--- a/android/app/src/main/assets/assets/BPO-Intelligence-Hub-Excel-Template.xlsx
+++ b/android/app/src/main/assets/assets/BPO-Intelligence-Hub-Excel-Template.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'README'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Projects'!$A$1:$O$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Clients'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SalaryFees'!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SalaryFees'!$A$1:$Q$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Leads'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -548,59 +548,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>positions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>headcount</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>salary</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>salaryUnit</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>feeUnit</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>taxRate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>DEMO - Nhà máy giả lập</t>
@@ -634,19 +658,32 @@
           <t>Thuê ngoài nhân sự</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Theo tháng (VNĐ/tháng)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>VNĐ/người/tháng</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>MẪU - không phải dự án thật</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:O2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -719,7 +756,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>DEMO - Doanh nghiệp logistics giả lập</t>
@@ -745,8 +781,6 @@
           <t>Cần xác minh</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>MẪU - không phải khách hàng thật</t>
@@ -765,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -785,339 +819,151 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>position</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>salaryMin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>salaryMax</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>salaryUnit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>feeMin</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>feeMax</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>feeUnit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>taxRate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>sourceUrl</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>updated</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Công nhân sản xuất</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Công nhân sản xuất</t>
+          <t>Bình Dương</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bình Dương</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>Sản xuất</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Theo tháng (VNĐ/tháng)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>VNĐ/người/tháng</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Lương gross/tháng</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Tin tuyển dụng công khai</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=tuy%E1%BB%83n+c%C3%B4ng+nh%C3%A2n+B%C3%ACnh+D%C6%B0%C6%A1ng</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Cần xác minh</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>MẪU - điền lương sau khi mở và xác minh tin tuyển dụng</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nhân viên kho / đóng gói</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bình Dương</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Logistics</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Lương gross/tháng</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Tin tuyển dụng công khai</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=tuy%E1%BB%83n+nh%C3%A2n+vi%C3%AAn+kho+B%C3%ACnh+D%C6%B0%C6%A1ng</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Cần xác minh</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>MẪU - ghi thêm ca, phụ cấp, tăng ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Nhân viên vệ sinh công nghiệp</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TP. Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Facility Management</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Lương gross/tháng</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Tin tuyển dụng công khai</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=tuy%E1%BB%83n+v%E1%BB%87+sinh+c%C3%B4ng+nghi%E1%BB%87p+TPHCM</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cần xác minh</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>MẪU - ghi thêm ca và định mức</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bảo vệ / an ninh</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>An ninh</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Lương gross/tháng</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Tin tuyển dụng công khai</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=tuy%E1%BB%83n+b%E1%BA%A3o+v%E1%BB%87+H%C3%A0+N%E1%BB%99i</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Cần xác minh</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MẪU - ghi rõ ca 8/12 giờ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nhân viên CSKH / tổng đài</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TP. Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Dịch vụ khách hàng</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Lương gross/tháng</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Tin tuyển dụng công khai</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=tuy%E1%BB%83n+CSKH+TPHCM</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Cần xác minh</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MẪU - ghi rõ KPI/ngoại ngữ</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:Q2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1220,7 +1066,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>DEMO - Cơ hội tuyển dụng giả lập</t>
@@ -1256,8 +1101,6 @@
           <t>https://www.google.com/search?q=tuy%E1%BB%83n+c%C3%B4ng+nh%C3%A2n+B%C3%ACnh+D%C6%B0%C6%A1ng</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>2</v>
       </c>
